--- a/data/trans_bre/P1417-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/P1417-Provincia-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4,53</t>
+          <t>3,32</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>449,33%</t>
+          <t>341,64%</t>
         </is>
       </c>
     </row>
@@ -660,22 +660,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,35; 0,82</t>
+          <t>-1,97; 0,83</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,75; 5,63</t>
+          <t>0,57; 5,24</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-0,27; 4,68</t>
+          <t>-0,31; 4,66</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2,01; 10,45</t>
+          <t>1,3; 6,53</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -685,17 +685,17 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-9,53; —</t>
+          <t>-24,77; —</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-71,95; —</t>
+          <t>-65,22; —</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>51,44; 2387,46</t>
+          <t>42,43; 1778,01</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>3,23</t>
+          <t>3,0</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>423,14%</t>
+          <t>391,44%</t>
         </is>
       </c>
     </row>
@@ -760,22 +760,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,62; 3,36</t>
+          <t>0,53; 3,39</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,95; 3,42</t>
+          <t>0,99; 3,42</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-1,23; 1,07</t>
+          <t>-1,24; 1,15</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,58; 4,95</t>
+          <t>1,52; 4,69</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -790,12 +790,12 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-86,8; 469,07</t>
+          <t>-88,52; 423,49</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>81,88; 1643,34</t>
+          <t>57,25; 1714,18</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2,19</t>
+          <t>2,24</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>191,03%</t>
+          <t>195,74%</t>
         </is>
       </c>
     </row>
@@ -860,22 +860,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,3</t>
+          <t>0,27; 2,33</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,26; 3,08</t>
+          <t>-0,34; 3,01</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,54; 3,81</t>
+          <t>0,54; 3,78</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,55; 3,86</t>
+          <t>0,55; 4,1</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-54,87; —</t>
+          <t>-66,06; —</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>22,02; 767,34</t>
+          <t>16,09; 748,99</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>2,32</t>
+          <t>3,14</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>185,56%</t>
+          <t>246,82%</t>
         </is>
       </c>
     </row>
@@ -960,22 +960,22 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-0,05; 2,35</t>
+          <t>-0,05; 2,31</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,53; 6,69</t>
+          <t>2,4; 6,83</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,63; 5,27</t>
+          <t>0,29; 5,15</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,52; 4,55</t>
+          <t>1,27; 5,37</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>6,98; 1331,92</t>
+          <t>-4,75; 1284,29</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>15,54; 673,17</t>
+          <t>39,74; 840,99</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2,78</t>
+          <t>2,77</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>495,11%</t>
+          <t>547,78%</t>
         </is>
       </c>
     </row>
@@ -1060,22 +1060,22 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,39; 5,85</t>
+          <t>0,61; 5,71</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,63; 7,97</t>
+          <t>0,58; 8,1</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,46; 5,28</t>
+          <t>0,41; 5,73</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,25; 4,66</t>
+          <t>1,16; 4,67</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1085,7 +1085,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-10,05; 1928,46</t>
+          <t>-6,12; 1693,09</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1095,7 +1095,7 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-9,47; —</t>
+          <t>31,99; —</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2,02</t>
+          <t>1,9</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>55,63%</t>
+          <t>52,97%</t>
         </is>
       </c>
     </row>
@@ -1160,22 +1160,22 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,36; 2,95</t>
+          <t>0,36; 2,98</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-0,74; 2,87</t>
+          <t>-0,73; 2,86</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-1,14; 2,58</t>
+          <t>-1,22; 2,6</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-0,65; 4,86</t>
+          <t>-0,92; 4,36</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1185,17 +1185,17 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
+          <t>-100,0; —</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>-100,0; —</t>
-        </is>
-      </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-20,12; 188,94</t>
+          <t>-19,12; 177,15</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>4,88</t>
+          <t>7,05</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>280,55%</t>
+          <t>344,32%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,74; 3,56</t>
+          <t>0,59; 3,36</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,36; 4,35</t>
+          <t>1,47; 4,78</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,43; 4,27</t>
+          <t>1,45; 4,2</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1,12; 7,65</t>
+          <t>5,01; 9,37</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>36,63; 1689,15</t>
+          <t>4,58; 1501,38</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>103,42; —</t>
+          <t>138,65; —</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>117,77; 2583,19</t>
+          <t>145,27; 3219,03</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>47,38; 655,64</t>
+          <t>167,89; 693,27</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>1,17</t>
+          <t>1,07</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>430,06%</t>
+          <t>301,7%</t>
         </is>
       </c>
     </row>
@@ -1360,32 +1360,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-0,01; 2,08</t>
+          <t>0,02; 2,28</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,45; 2,76</t>
+          <t>0,5; 2,74</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1,46; 3,74</t>
+          <t>1,44; 3,82</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0,52; 2,18</t>
+          <t>0,32; 2,17</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-29,35; 710,26</t>
+          <t>-10,44; 971,38</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>24,82; 1497,72</t>
+          <t>21,89; 1474,0</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -1395,7 +1395,7 @@
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>24,53; 2466,13</t>
+          <t>18,88; 2221,37</t>
         </is>
       </c>
     </row>
@@ -1427,7 +1427,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>3,07</t>
+          <t>3,28</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1447,7 +1447,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>273,35%</t>
+          <t>264,28%</t>
         </is>
       </c>
     </row>
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,82; 1,83</t>
+          <t>0,8; 1,82</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>1,72; 2,97</t>
+          <t>1,71; 2,91</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1,33; 2,51</t>
+          <t>1,32; 2,5</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>2,19; 3,86</t>
+          <t>2,6; 3,89</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>119,47; 735,4</t>
+          <t>125,2; 667,35</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>268,3; 1093,33</t>
+          <t>267,68; 970,2</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>168,04; 658,49</t>
+          <t>167,1; 647,38</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>157,51; 425,18</t>
+          <t>164,03; 383,6</t>
         </is>
       </c>
     </row>
